--- a/performance_data_graphite/test/metrics.xlsx
+++ b/performance_data_graphite/test/metrics.xlsx
@@ -468,7 +468,7 @@
         <v>2.42439045564755</v>
       </c>
       <c r="E2" t="n">
-        <v>3.76717586879478</v>
+        <v>7.531573581024019</v>
       </c>
     </row>
     <row r="3">
@@ -489,7 +489,7 @@
         <v>0.7142553960804113</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2222155480212936</v>
+        <v>1.071297985088352</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         <v>4.192071531771325</v>
       </c>
       <c r="E4" t="n">
-        <v>2.879356753412596</v>
+        <v>2.919163653887923</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         <v>13.94359296994845</v>
       </c>
       <c r="E5" t="n">
-        <v>2.414873460591368</v>
+        <v>6.536388576156781</v>
       </c>
     </row>
     <row r="6">
@@ -552,7 +552,7 @@
         <v>1.358290118541781</v>
       </c>
       <c r="E6" t="n">
-        <v>1.120561001063206</v>
+        <v>2.595029601735988</v>
       </c>
     </row>
     <row r="7">
@@ -573,7 +573,7 @@
         <v>7.971354479365974</v>
       </c>
       <c r="E7" t="n">
-        <v>1.136783966428413</v>
+        <v>5.720493108369614</v>
       </c>
     </row>
     <row r="8">
@@ -594,7 +594,7 @@
         <v>1207.743953141724</v>
       </c>
       <c r="E8" t="n">
-        <v>1209.427520445399</v>
+        <v>1209.308205902918</v>
       </c>
     </row>
   </sheetData>
